--- a/public/upload/export_excel/all-06-2025.xlsx
+++ b/public/upload/export_excel/all-06-2025.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
   <si>
     <t>สาขาเจริญใจ</t>
   </si>
@@ -35,25 +35,25 @@
     <t>ค่าไฟฟ้า</t>
   </si>
   <si>
-    <t>ค่าเช่าเฟอร์นิเจอร์</t>
+    <t>ค่าที่จอดมอเตอร์ไซค์</t>
   </si>
   <si>
     <t>ค่าที่จอดรถยนต์</t>
   </si>
   <si>
-    <t>ค่าที่จอดมอเตอร์ไซค์</t>
-  </si>
-  <si>
-    <t>ส่วนกลาง</t>
-  </si>
-  <si>
-    <t>ค่าห้องพนักงาน</t>
-  </si>
-  <si>
-    <t>จดค่าน้ำผิด</t>
-  </si>
-  <si>
-    <t>หัก ภาษี</t>
+    <t>ค่าอินเตอร์เน็ต</t>
+  </si>
+  <si>
+    <t>ค่าเฟอร์นิเจอร์</t>
+  </si>
+  <si>
+    <t>ค่าซักผ้า</t>
+  </si>
+  <si>
+    <t>Orange Test</t>
+  </si>
+  <si>
+    <t>ส้ม</t>
   </si>
   <si>
     <t>รวม</t>
@@ -89,19 +89,46 @@
     <t>เบอร์โทร</t>
   </si>
   <si>
+    <t>A202</t>
+  </si>
+  <si>
+    <t>4,265</t>
+  </si>
+  <si>
+    <t>วรเวก ชึรัมย์</t>
+  </si>
+  <si>
+    <t>ต.บางพลีใหญ่ อ.บางพลี จ.สมุทรปราการ</t>
+  </si>
+  <si>
+    <t>0987776543</t>
+  </si>
+  <si>
+    <t>A201</t>
+  </si>
+  <si>
+    <t>3,465</t>
+  </si>
+  <si>
+    <t>A108</t>
+  </si>
+  <si>
+    <t>5,465</t>
+  </si>
+  <si>
+    <t>A106</t>
+  </si>
+  <si>
+    <t>ฉัน กำไล</t>
+  </si>
+  <si>
     <t>A105</t>
   </si>
   <si>
     <t>5,665</t>
   </si>
   <si>
-    <t>กู ชึรัมย์</t>
-  </si>
-  <si>
-    <t>ต.บางพลีใหญ่ อ.บางพลี จ.สมุทรปราการ</t>
-  </si>
-  <si>
-    <t>0987776543</t>
+    <t>wut ti</t>
   </si>
   <si>
     <t>A101</t>
@@ -110,9 +137,6 @@
     <t>5,495</t>
   </si>
   <si>
-    <t>วรเวก ชึรัมย์</t>
-  </si>
-  <si>
     <t>A107</t>
   </si>
   <si>
@@ -125,9 +149,6 @@
     <t>A103</t>
   </si>
   <si>
-    <t>5,465</t>
-  </si>
-  <si>
     <t>A102</t>
   </si>
   <si>
@@ -138,9 +159,6 @@
   </si>
   <si>
     <t>0641241254</t>
-  </si>
-  <si>
-    <t>Orange Test</t>
   </si>
   <si>
     <t>ต.บางกรวย อ.บางกรวย จ.นนทบุรี</t>
@@ -489,7 +507,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -617,21 +635,35 @@
         <v>24</v>
       </c>
       <c r="B4" s="1">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="C4" s="1">
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="D4" s="1">
         <v>105</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="E4" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>80.0</v>
+      </c>
       <c r="L4" s="1" t="s">
         <v>25</v>
       </c>
@@ -661,7 +693,7 @@
         <v>29</v>
       </c>
       <c r="B5" s="1">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="C5" s="1">
         <v>270</v>
@@ -669,13 +701,27 @@
       <c r="D5" s="1">
         <v>105</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="E5" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>80.0</v>
+      </c>
       <c r="L5" s="1" t="s">
         <v>30</v>
       </c>
@@ -689,7 +735,7 @@
         <v>456</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>27</v>
@@ -702,7 +748,7 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1">
         <v>5000</v>
@@ -713,15 +759,29 @@
       <c r="D6" s="1">
         <v>105</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
+      <c r="E6" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>80.0</v>
+      </c>
       <c r="L6" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -733,7 +793,7 @@
         <v>456</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>27</v>
@@ -757,15 +817,29 @@
       <c r="D7" s="1">
         <v>105</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+      <c r="E7" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>80.0</v>
+      </c>
       <c r="L7" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -777,7 +851,7 @@
         <v>456</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>27</v>
@@ -801,13 +875,27 @@
       <c r="D8" s="1">
         <v>105</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+      <c r="E8" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>80.0</v>
+      </c>
       <c r="L8" s="1" t="s">
         <v>36</v>
       </c>
@@ -821,7 +909,7 @@
         <v>456</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>27</v>
@@ -834,7 +922,7 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="1">
         <v>5000</v>
@@ -845,15 +933,29 @@
       <c r="D9" s="1">
         <v>105</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
+      <c r="E9" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>80.0</v>
+      </c>
       <c r="L9" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -865,20 +967,20 @@
         <v>456</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B10" s="1">
         <v>5000</v>
@@ -889,15 +991,29 @@
       <c r="D10" s="1">
         <v>105</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+      <c r="E10" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>80.0</v>
+      </c>
       <c r="L10" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -909,15 +1025,247 @@
         <v>456</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
       <c r="V10" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C11" s="1">
+        <v>270</v>
+      </c>
+      <c r="D11" s="1">
+        <v>105</v>
+      </c>
+      <c r="E11" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1">
+        <v>15</v>
+      </c>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1">
+        <v>456</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" s="1" t="s">
         <v>43</v>
+      </c>
+      <c r="B12" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C12" s="1">
+        <v>270</v>
+      </c>
+      <c r="D12" s="1">
+        <v>105</v>
+      </c>
+      <c r="E12" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1">
+        <v>15</v>
+      </c>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1">
+        <v>456</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C13" s="1">
+        <v>270</v>
+      </c>
+      <c r="D13" s="1">
+        <v>105</v>
+      </c>
+      <c r="E13" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1">
+        <v>15</v>
+      </c>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1">
+        <v>456</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C14" s="1">
+        <v>270</v>
+      </c>
+      <c r="D14" s="1">
+        <v>105</v>
+      </c>
+      <c r="E14" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1">
+        <v>15</v>
+      </c>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1">
+        <v>456</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
